--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iteration 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iteration 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Iteration 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Iteration 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,11 +64,11 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00065F46"/>
+      <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00991B1B"/>
+      <color rgb="00065F46"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -121,12 +121,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F5E8"/>
+        <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD5D5"/>
+        <fgColor rgb="00D5F5E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -644,14 +644,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -670,15 +663,15 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Amped Up!
-Reshma Sharma
-48% pred | 48% hist
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Back Body Blaze
 Anisha Shah
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -692,56 +685,56 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Reshma Sharma
-38% pred | 0% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
@@ -780,18 +773,18 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Rohan Dahima
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -823,11 +816,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-42% pred | 42% hist
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -848,11 +841,11 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Rohan Dahima
-43% pred | 43% hist
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -863,7 +856,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Recovery
 Reshma Sharma
@@ -878,10 +871,10 @@
           <t>Mat 57
 Anisha Shah
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Recovery
 Atulan Purohit
@@ -889,13 +882,27 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Recovery
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -903,20 +910,20 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -924,54 +931,124 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab
+Atulan Purohit
 52% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab
+Atulan Purohit
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-38% pred | 0% hist
-[DROP]</t>
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H13" s="5" t="n"/>
@@ -979,22 +1056,22 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-40% pred | 40% hist
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1006,7 +1083,56 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Mrigakshi Jaiswal
@@ -1014,73 +1140,17 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Atulan Purohit
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Atulan Purohit
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
+          <t>Barre 57
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -1091,163 +1161,72 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-26% pred | 26% hist
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-63% pred | 63% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1263,7 +1242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1350,14 +1329,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -1376,15 +1348,15 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Amped Up!
-Reshma Sharma
-48% pred | 48% hist
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Back Body Blaze
 Anisha Shah
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -1398,56 +1370,56 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Reshma Sharma
-38% pred | 0% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
@@ -1486,18 +1458,18 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Rohan Dahima
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -1529,11 +1501,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-42% pred | 42% hist
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1554,11 +1526,11 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Rohan Dahima
-43% pred | 43% hist
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1569,7 +1541,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Recovery
 Reshma Sharma
@@ -1584,10 +1556,10 @@
           <t>Mat 57
 Anisha Shah
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Recovery
 Atulan Purohit
@@ -1595,13 +1567,27 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Recovery
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -1609,20 +1595,20 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -1630,54 +1616,124 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab
+Atulan Purohit
 52% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab
+Atulan Purohit
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-38% pred | 0% hist
-[DROP]</t>
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H13" s="5" t="n"/>
@@ -1685,22 +1741,22 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-40% pred | 40% hist
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1712,7 +1768,56 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Mrigakshi Jaiswal
@@ -1720,73 +1825,17 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Atulan Purohit
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Atulan Purohit
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
+          <t>Barre 57
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -1797,163 +1846,72 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-26% pred | 26% hist
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-63% pred | 63% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1969,7 +1927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2056,14 +2014,7 @@
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -2082,15 +2033,15 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Amped Up!
-Reshma Sharma
-48% pred | 48% hist
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Back Body Blaze
 Anisha Shah
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -2104,56 +2055,56 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Reshma Sharma
-38% pred | 0% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
@@ -2192,18 +2143,18 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Rohan Dahima
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -2235,11 +2186,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-42% pred | 42% hist
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2260,11 +2211,11 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Rohan Dahima
-43% pred | 43% hist
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2275,7 +2226,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Recovery
 Reshma Sharma
@@ -2290,10 +2241,10 @@
           <t>Mat 57
 Anisha Shah
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Recovery
 Atulan Purohit
@@ -2301,13 +2252,27 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Recovery
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -2315,20 +2280,20 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -2336,54 +2301,124 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab
+Atulan Purohit
 52% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Strength Lab
+Atulan Purohit
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-38% pred | 0% hist
-[DROP]</t>
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H13" s="5" t="n"/>
@@ -2391,22 +2426,22 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-40% pred | 40% hist
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2418,7 +2453,56 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Mrigakshi Jaiswal
@@ -2426,73 +2510,17 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Atulan Purohit
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Atulan Purohit
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Recovery
+          <t>Barre 57
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Pranjali Jain
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -2503,163 +2531,72 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-26% pred | 26% hist
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Reshma Sharma
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-63% pred | 63% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Mrigakshi Jaiswal
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -56,10 +56,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="001E3A8A"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <color rgb="00831843"/>
       <sz val="9"/>
     </font>
@@ -69,6 +65,10 @@
     </font>
     <font>
       <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="001E3A8A"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -111,11 +111,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E4FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFD5F0"/>
       </patternFill>
     </fill>
@@ -127,6 +122,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFD5D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E4FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -635,21 +635,14 @@
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
+          <t>Barre 57
 Reshma Sharma
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -660,28 +653,28 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-48% pred | 48% hist
+60% pred | 60% hist
 [PROTECT]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[PROTECT]</t>
+          <t>Cardio Barre
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -716,20 +709,20 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
 Atulan Purohit
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anisha Shah
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -779,31 +772,39 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>HIIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
+Anisha Shah
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>HIIT
 Anisha Shah
@@ -811,7 +812,6 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
@@ -821,27 +821,27 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>HIIT
 Rohan Dahima
 38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+42% pred | 42% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -853,14 +853,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
+      <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -884,7 +877,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -908,10 +901,17 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -973,7 +973,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Reshma Sharma
@@ -997,27 +997,27 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-38% pred | 38% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-38% pred | 0% hist
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+83% pred | 83% hist
 [PROTECT]</t>
         </is>
       </c>
@@ -1045,7 +1045,7 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -1053,15 +1053,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 38% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -1069,11 +1069,11 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-83% pred | 83% hist
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
 [PROTECT]</t>
         </is>
       </c>
@@ -1085,7 +1085,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -1109,17 +1109,17 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
 Pranjali Jain
 38% pred | 0% hist
 [PROTECT]</t>
@@ -1133,7 +1133,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -1158,20 +1158,20 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-39% pred | 39% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+42% pred | 42% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1209,16 +1209,16 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Rohan Dahima
-38% pred | 0% hist
+          <t>Barre 57
+Rohan Dahima
+63% pred | 63% hist
 [PROTECT]</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
+          <t>Back Body Blaze
+Anisha Shah
 38% pred | 0% hist
 [PROTECT]</t>
         </is>
@@ -1241,7 +1241,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1348,21 +1348,14 @@
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
+          <t>Barre 57
 Reshma Sharma
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -1373,28 +1366,28 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-48% pred | 48% hist
+60% pred | 60% hist
 [PROTECT]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[PROTECT]</t>
+          <t>Cardio Barre
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -1429,20 +1422,20 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
 Atulan Purohit
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anisha Shah
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1492,31 +1485,39 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>HIIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
+Anisha Shah
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>HIIT
 Anisha Shah
@@ -1524,7 +1525,6 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
@@ -1534,27 +1534,27 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>HIIT
 Rohan Dahima
 38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+42% pred | 42% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1566,14 +1566,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
+      <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1597,7 +1590,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -1621,10 +1614,17 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1686,7 +1686,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Reshma Sharma
@@ -1710,27 +1710,27 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-38% pred | 38% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-38% pred | 0% hist
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+83% pred | 83% hist
 [PROTECT]</t>
         </is>
       </c>
@@ -1758,7 +1758,7 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -1766,15 +1766,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 38% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -1782,11 +1782,11 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-83% pred | 83% hist
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
 [PROTECT]</t>
         </is>
       </c>
@@ -1798,7 +1798,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -1822,17 +1822,17 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
 Pranjali Jain
 38% pred | 0% hist
 [PROTECT]</t>
@@ -1846,7 +1846,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -1871,20 +1871,20 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-39% pred | 39% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+42% pred | 42% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1922,16 +1922,16 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Rohan Dahima
-38% pred | 0% hist
+          <t>Barre 57
+Rohan Dahima
+63% pred | 63% hist
 [PROTECT]</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
+          <t>Back Body Blaze
+Anisha Shah
 38% pred | 0% hist
 [PROTECT]</t>
         </is>
@@ -1954,7 +1954,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -2061,21 +2061,14 @@
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
+          <t>Barre 57
 Reshma Sharma
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -2086,28 +2079,28 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Amped Up!
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
-48% pred | 48% hist
+60% pred | 60% hist
 [PROTECT]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Anisha Shah
-38% pred | 0% hist
-[PROTECT]</t>
+          <t>Cardio Barre
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -2142,20 +2135,20 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
 Atulan Purohit
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anisha Shah
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -2205,31 +2198,39 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Anisha Shah
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>HIIT
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
+Anisha Shah
+38% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>HIIT
 Anisha Shah
@@ -2237,7 +2238,6 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
@@ -2247,27 +2247,27 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>HIIT
 Rohan Dahima
 38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+42% pred | 42% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2279,14 +2279,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
+      <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2310,7 +2303,7 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -2334,10 +2327,17 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2399,7 +2399,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Reshma Sharma
@@ -2423,27 +2423,27 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-38% pred | 38% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-38% pred | 0% hist
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+83% pred | 83% hist
 [PROTECT]</t>
         </is>
       </c>
@@ -2471,7 +2471,7 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -2479,15 +2479,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 38% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -2495,11 +2495,11 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-83% pred | 83% hist
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+38% pred | 0% hist
 [PROTECT]</t>
         </is>
       </c>
@@ -2511,7 +2511,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Pranjali Jain
@@ -2535,17 +2535,17 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
 Pranjali Jain
 38% pred | 0% hist
 [PROTECT]</t>
@@ -2559,7 +2559,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -2584,20 +2584,20 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anisha Shah
-39% pred | 39% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+42% pred | 42% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -2635,16 +2635,16 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Rohan Dahima
-38% pred | 0% hist
+          <t>Barre 57
+Rohan Dahima
+63% pred | 63% hist
 [PROTECT]</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
+          <t>Back Body Blaze
+Anisha Shah
 38% pred | 0% hist
 [PROTECT]</t>
         </is>
@@ -2667,7 +2667,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="006B21A8"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
@@ -53,10 +57,6 @@
     </font>
     <font>
       <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
     <font>
@@ -71,8 +71,12 @@
       <color rgb="00374151"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +91,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,11 +120,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFD5F0"/>
       </patternFill>
     </fill>
@@ -127,6 +131,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -170,15 +179,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -190,6 +199,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -557,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -629,12 +641,33 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Rohan Dahima
+21% pred | 21% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -642,18 +675,18 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -661,23 +694,23 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-36% pred | 36% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-38% pred | 38% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+60% pred | 60% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+8% pred | 8% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>HIIT
 Rohan Dahima
@@ -685,55 +718,55 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
 40% pred | 40% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Richard D'Costa
+Pranjali Jain
 25% pred | 25% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Rohan Dahima
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Pranjali Jain
+44% pred | 44% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pranjali Jain
 54% pred | 54% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Karanvir Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-54% pred | 54% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -741,34 +774,34 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>FIT
-Anisha Shah
+Mrigakshi Jaiswal
 62% pred | 62% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
 55% pred | 55% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -776,49 +809,49 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Anisha Shah
+38% pred | 38% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
 Rohan Dahima
 20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
-Vivaran Dhasmana
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-53% pred | 53% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+Rohan Dahima
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -826,68 +859,68 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Karanvir Bhatia
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Richard D'Costa
-27% pred | 27% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Anisha Shah
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+Pranjali Jain
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Rohan Dahima
@@ -895,15 +928,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -911,30 +944,54 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+43% pred | 43% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Atulan Purohit
-63% pred | 63% hist
-[DROP]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
+Rohan Dahima
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Rohan Dahima
-10% pred | 10% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Amped Up!
 Richard D'Costa
@@ -942,87 +999,63 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Rohan Dahima
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Mrigakshi Jaiswal
-34% pred | 34% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-57% pred | 57% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-52% pred | 52% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Anisha Shah
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1030,12 +1063,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-81% pred | 81% hist
-[PROTECT]</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 52% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -1045,16 +1078,16 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>FIT
-Karanvir Bhatia
+          <t>Mat 57 Express
+Karan Bhatia
 20% pred | 0% hist
 [INCLUDE]</t>
         </is>
@@ -1066,12 +1099,12 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>FIT
 Pranjali Jain
@@ -1079,15 +1112,92 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Recovery
+Atulan Purohit
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Cauveri Vikrant
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+100% pred | 100% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1095,7 +1205,63 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+62% pred | 62% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 20% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Karanvir Bhatia
+54% pred | 54% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+44% pred | 44% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+34% pred | 34% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab
+Atulan Purohit
+20% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Anisha Shah
@@ -1103,47 +1269,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 20% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Karan Bhatia
-46% pred | 46% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-44% pred | 44% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -1151,55 +1277,39 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+82% pred | 82% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
 Cauveri Vikrant
-62% pred | 62% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab
-Atulan Purohit
-20% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-82% pred | 82% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-65% pred | 65% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+20% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1207,31 +1317,31 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
+Vivaran Dhasmana
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
 65% pred | 65% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Vivaran Dhasmana
-24% pred | 24% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Cauveri Vikrant
@@ -1239,23 +1349,23 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Karan Bhatia
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1263,15 +1373,15 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -1279,39 +1389,39 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-27% pred | 27% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
 Vivaran Dhasmana
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+49% pred | 49% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+22% pred | 22% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1319,7 +1429,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1327,7 +1437,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1335,39 +1445,39 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-43% pred | 43% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
 80% pred | 80% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
@@ -1375,40 +1485,47 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-63% pred | 63% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Atulan Purohit
+20% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
 31% pred | 31% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Cauveri Vikrant
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Atulan Purohit
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Karanvir Bhatia
-29% pred | 29% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Karan Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n"/>
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1424,7 +1541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1496,12 +1613,33 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+17% pred | 17% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1509,18 +1647,18 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1528,7 +1666,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Amped Up!
 Reshma Sharma
@@ -1536,71 +1674,71 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+38% pred | 38% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+40% pred | 40% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
 Vivaran Dhasmana
-38% pred | 38% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-25% pred | 25% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
+61% pred | 61% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Pranjali Jain
+44% pred | 44% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pranjali Jain
 54% pred | 54% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-25% pred | 25% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-54% pred | 54% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -1608,15 +1746,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>FIT
-Anisha Shah
+Mrigakshi Jaiswal
 62% pred | 62% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -1624,18 +1762,18 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1643,118 +1781,118 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anisha Shah
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
-Vivaran Dhasmana
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
+Rohan Dahima
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-53% pred | 53% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Raunak Khemuka
 20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Rohan Dahima
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Atulan Purohit
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Vivaran Dhasmana
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Anisha Shah
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Rohan Dahima
@@ -1762,15 +1900,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1778,7 +1916,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Atulan Purohit
@@ -1787,29 +1925,29 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Richard D'Costa
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Atulan Purohit
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Reshma Sharma
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Rohan Dahima
@@ -1817,45 +1955,31 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
 Mrigakshi Jaiswal
-34% pred | 34% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
 Richard D'Costa
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
+29% pred | 29% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1865,7 +1989,7 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -1878,11 +2002,32 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+34% pred | 34% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Rohan Dahima
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1890,27 +2035,48 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-81% pred | 81% hist
-[PROTECT]</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+52% pred | 52% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>FIT
 Pranjali Jain
@@ -1918,15 +2084,92 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Rohan Dahima
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+100% pred | 100% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1934,15 +2177,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anisha Shah
-67% pred | 67% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+62% pred | 62% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1950,7 +2193,7 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Barre 57 Express
 Karanvir Bhatia
@@ -1958,31 +2201,31 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-65% pred | 65% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+41% pred | 41% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+34% pred | 34% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -1990,15 +2233,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-40% pred | 40% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+75% pred | 75% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -2006,111 +2249,111 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
 82% pred | 82% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anisha Shah
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Cauveri Vikrant
+20% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+34% pred | 34% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>FIT
 Atulan Purohit
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
 Vivaran Dhasmana
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-32% pred | 32% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
 65% pred | 65% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
-Vivaran Dhasmana
-24% pred | 24% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Vivaran Dhasmana
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+Atulan Purohit
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Amped Up!
 Atulan Purohit
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Atulan Purohit
@@ -2118,39 +2361,39 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+32% pred | 32% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Vivaran Dhasmana
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Atulan Purohit
-20% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+Karanvir Bhatia
+67% pred | 67% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -2158,7 +2401,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2166,7 +2409,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2174,7 +2417,7 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -2182,7 +2425,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2190,64 +2433,71 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Pranjali Jain
-39% pred | 39% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-29% pred | 29% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
 31% pred | 31% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Richard D'Costa
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>HIIT
 Karan Bhatia
-18% pred | 18% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Karan Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2263,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2338,20 +2588,20 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-48% pred | 48% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Anisha Shah
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -2359,9 +2609,9 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2369,18 +2619,18 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2388,12 +2638,12 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Reshma Sharma
-48% pred | 48% hist
-[INCLUDE]</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+25% pred | 25% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -2404,39 +2654,39 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Cauveri Vikrant
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Rohan Dahima
+47% pred | 47% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
 40% pred | 40% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-80% pred | 80% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre Express
 Pranjali Jain
@@ -2447,20 +2697,20 @@
       <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Richard D'Costa
-100% pred | 100% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+Pranjali Jain
+44% pred | 44% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Anisha Shah
+Karanvir Bhatia
 54% pred | 54% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -2468,23 +2718,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>FIT
-Anisha Shah
+Mrigakshi Jaiswal
 62% pred | 62% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Pranjali Jain
-17% pred | 17% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+55% pred | 55% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -2492,10 +2742,10 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2503,12 +2753,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2521,15 +2771,15 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Pranjali Jain
@@ -2537,15 +2787,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -2556,12 +2806,12 @@
       <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Cauveri Vikrant
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
+Richard D'Costa
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -2569,28 +2819,28 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Karanvir Bhatia
+Karan Bhatia
 20% pred | 0% hist
 [INCLUDE]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2598,11 +2848,11 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Reshma Sharma
-20% pred | 0% hist
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Pranjali Jain
+31% pred | 31% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2614,7 +2864,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Rohan Dahima
@@ -2622,15 +2872,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2638,22 +2888,22 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-55% pred | 55% hist
-[DROP]</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+90% pred | 90% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Amped Up!
 Rohan Dahima
@@ -2661,15 +2911,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Richard D'Costa
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Anisha Shah
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
@@ -2677,24 +2927,31 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Richard D'Costa
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Cauveri Vikrant
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Anisha Shah
-57% pred | 57% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -2704,45 +2961,45 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-14% pred | 14% hist
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+20% pred | 20% hist
 [INCLUDE]</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
+          <t>Strength Lab (Pull)
+Reshma Sharma
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
           <t>Strength Lab (Push)
-Reshma Sharma
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab
+Rohan Dahima
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
 Mrigakshi Jaiswal
 20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2750,7 +3007,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2765,13 +3022,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2786,47 +3043,75 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-65% pred | 65% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Recovery
+Cauveri Vikrant
+17% pred | 17% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Recovery
+Atulan Purohit
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+10% pred | 10% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Vivaran Dhasmana
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
@@ -2834,15 +3119,15 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -2850,15 +3135,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Anisha Shah
-67% pred | 67% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+40% pred | 40% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2866,23 +3151,23 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Barre 57 Express
-Richard D'Costa
-56% pred | 56% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-37% pred | 37% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+Karanvir Bhatia
+54% pred | 54% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+44% pred | 44% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2890,15 +3175,15 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -2906,15 +3191,15 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-40% pred | 40% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Atulan Purohit
+100% pred | 100% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Strength Lab
 Atulan Purohit
@@ -2922,39 +3207,39 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
 82% pred | 82% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-65% pred | 65% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+Anisha Shah
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Mat 57 Express
-Vivaran Dhasmana
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+Karanvir Bhatia
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2962,31 +3247,31 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
 Vivaran Dhasmana
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
 65% pred | 65% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Vivaran Dhasmana
-24% pred | 24% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
 Atulan Purohit
@@ -2994,23 +3279,16 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Cauveri Vikrant
@@ -3018,23 +3296,23 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Cauveri Vikrant
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Atulan Purohit
-35% pred | 35% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
+Vivaran Dhasmana
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
@@ -3042,31 +3320,31 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Atulan Purohit
-22% pred | 22% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+67% pred | 67% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -3074,7 +3352,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -3082,7 +3360,7 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -3090,15 +3368,15 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>HIIT
-Karan Bhatia
-18% pred | 18% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -3106,23 +3384,23 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
 Atulan Purohit
@@ -3130,39 +3408,39 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Atulan Purohit
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-29% pred | 29% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Vivaran Dhasmana
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Atulan Purohit
+43% pred | 43% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Cauveri Vikrant
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>HIIT
 Karan Bhatia
@@ -3170,7 +3448,28 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -707,14 +707,7 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
@@ -735,9 +728,9 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Amped Up!
-Reshma Sharma
-48% pred | 0% hist
+          <t>Barre 57
+Karanvir Bhatia
+25% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -866,7 +859,14 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
@@ -904,30 +904,9 @@
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -935,7 +914,14 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
@@ -966,7 +952,14 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -996,11 +989,11 @@
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-72% pred | 0% hist
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+73% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1101,17 +1094,17 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Barre 57 Express
+          <t>Cardio Barre
+Reshma Sharma
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Karanvir Bhatia
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-43% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1140,14 +1133,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Pranjali Jain
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1156,14 +1142,7 @@
 []</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-64% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -1184,14 +1163,7 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
     </row>
@@ -1274,12 +1246,19 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-22% pred | 0% hist
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1324,7 +1303,14 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>
@@ -1504,14 +1490,7 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
@@ -1532,9 +1511,9 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Amped Up!
-Reshma Sharma
-48% pred | 0% hist
+          <t>Barre 57
+Karanvir Bhatia
+25% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1663,7 +1642,14 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
@@ -1701,30 +1687,9 @@
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -1732,7 +1697,14 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
@@ -1763,7 +1735,14 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -1793,11 +1772,11 @@
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-72% pred | 0% hist
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+73% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1898,17 +1877,17 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Barre 57 Express
+          <t>Cardio Barre
+Reshma Sharma
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Karanvir Bhatia
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-43% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1937,14 +1916,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Pranjali Jain
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1953,14 +1925,7 @@
 []</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-64% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -1981,14 +1946,7 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
     </row>
@@ -2071,12 +2029,19 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-22% pred | 0% hist
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2121,7 +2086,14 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>
@@ -2301,14 +2273,7 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
@@ -2329,9 +2294,9 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Amped Up!
-Reshma Sharma
-48% pred | 0% hist
+          <t>Barre 57
+Karanvir Bhatia
+25% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2460,7 +2425,14 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Karanvir Bhatia
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
@@ -2498,30 +2470,9 @@
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-73% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -2529,7 +2480,14 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
@@ -2560,7 +2518,14 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -2590,11 +2555,11 @@
       </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Reshma Sharma
-72% pred | 0% hist
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+73% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2695,17 +2660,17 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Barre 57 Express
+          <t>Cardio Barre
+Reshma Sharma
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Karanvir Bhatia
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-43% pred | 0% hist
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2734,14 +2699,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Pranjali Jain
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2750,14 +2708,7 @@
 []</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-64% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
@@ -2778,14 +2729,7 @@
 []</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
     </row>
@@ -2868,12 +2812,19 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-22% pred | 0% hist
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2918,7 +2869,14 @@
 []</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+67% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -55,20 +55,20 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
+      <color rgb="00831843"/>
       <sz val="9"/>
     </font>
     <font>
       <color rgb="00374151"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="00831843"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -111,22 +111,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFD5F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD5F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,10 +181,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kwality House, Kemps Corner  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Kwality House, Kemps Corner  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -586,43 +586,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
         <is>
           <t>PowerCycle
 Bret Saldanha
-41% pred | 41% hist
+40% pred | 40% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -670,7 +670,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
@@ -695,7 +702,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-63% pred | 63% hist
+64% pred | 64% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -704,17 +711,17 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -725,139 +732,167 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
+          <t>HIIT
+Mrigakshi Jaiswal
+47% pred | 47% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
           <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n"/>
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Atulan Purohit
+67% pred | 67% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 64% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+51% pred | 51% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
 Pranjali Jain
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simonelle De Vitre
-46% pred | 46% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Bret Saldanha
-0% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
-62% pred | 62% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
 24% pred | 24% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+18% pred | 18% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -865,9 +900,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -875,42 +910,49 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Rohan Dahima
-73% pred | 73% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+Reshma Sharma
+71% pred | 71% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Pranjali Jain
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
-Simonelle De Vitre
-28% pred | 28% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-54% pred | 54% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="10" t="inlineStr">
+Atulan Purohit
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Simran Dutt
@@ -918,23 +960,16 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -942,62 +977,6 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -1007,49 +986,56 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-73% pred | 73% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Mrigakshi Jaiswal
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>16:30</t>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
@@ -1057,11 +1043,11 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1070,7 +1056,7 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -1078,23 +1064,44 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-29% pred | 29% hist
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+28% pred | 28% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Simonelle De Vitre
@@ -1102,15 +1109,15 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
-38% pred | 38% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+37% pred | 37% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -1118,7 +1125,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Simonelle De Vitre
@@ -1126,25 +1133,17 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Simran Dutt
@@ -1152,36 +1151,37 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Pranjali Jain
-55% pred | 55% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-37% pred | 37% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
 Richard D'Costa
@@ -1189,19 +1189,19 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1209,9 +1209,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Richard D'Costa
@@ -1219,44 +1219,44 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-57% pred | 57% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
 Simonelle De Vitre
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -1264,7 +1264,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -1272,7 +1272,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Simonelle De Vitre
@@ -1280,32 +1280,18 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Karan Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anmol Sharma
@@ -1313,23 +1299,23 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-41% pred | 41% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>HIIT
 Richard D'Costa
-59% pred | 59% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
@@ -1337,15 +1323,8 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1356,810 +1335,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kwality House, Kemps Corner  |  Trainer Hours  |  Week of 2026-05-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Monday
-11-May</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday
-12-May</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday
-13-May</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Thursday
-14-May</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Friday
-15-May</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Saturday
-16-May</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Sunday
-17-May</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="52" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Anisha Shah
-88% pred | 88% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-41% pred | 41% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Anisha Shah
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Mrigakshi Jaiswal
-58% pred | 58% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-77% pred | 77% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-63% pred | 63% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Mrigakshi Jaiswal
-47% pred | 47% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-64% pred | 64% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Pranjali Jain
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-60% pred | 60% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-18% pred | 18% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-39% pred | 39% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Rohan Dahima
-73% pred | 73% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Raunak Khemuka
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-63% pred | 63% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-43% pred | 43% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-38% pred | 38% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simonelle De Vitre
-15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Richard D'Costa
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-57% pred | 57% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-43% pred | 43% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anmol Sharma
-83% pred | 83% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Richard D'Costa
-59% pred | 59% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-67% pred | 67% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2181,7 +1356,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kwality House, Kemps Corner  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Kwality House, Kemps Corner  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2194,43 +1369,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -2262,11 +1437,11 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-41% pred | 41% hist
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+46% pred | 46% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2278,7 +1453,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
@@ -2298,12 +1480,19 @@
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+76% pred | 76% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-63% pred | 63% hist
+64% pred | 64% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2312,31 +1501,52 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n"/>
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -2351,7 +1561,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-69% pred | 69% hist
+67% pred | 67% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2361,7 +1571,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -2370,48 +1580,41 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-64% pred | 64% hist
+51% pred | 51% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Pranjali Jain
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
+Atulan Purohit
+71% pred | 71% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simonelle De Vitre
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-48% pred | 48% hist
-[CONSIDER]</t>
+          <t>FIT
+Mrigakshi Jaiswal
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>FIT
-Anmol Sharma
-51% pred | 51% hist
-[INCLUDE]</t>
+          <t>Barre 57
+Simran Dutt
+24% pred | 24% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -2425,11 +1628,11 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-61% pred | 61% hist
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2438,7 +1641,7 @@
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2446,21 +1649,21 @@
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+18% pred | 18% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>FIT
 Cauveri Vikrant
-22% pred | 22% hist
-[CONSIDER]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -2501,17 +1704,17 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Richard D'Costa
-33% pred | 33% hist
-[INCLUDE]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2526,13 +1729,20 @@
         <is>
           <t>Cardio Barre
 Atulan Purohit
-40% pred | 40% hist
+39% pred | 39% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Simran Dutt
@@ -2540,7 +1750,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Raunak Khemuka
@@ -2550,21 +1760,35 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Pranjali Jain
+Atulan Purohit
 43% pred | 43% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2573,53 +1797,81 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Mrigakshi Jaiswal
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+73% pred | 73% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>FIT
 Raunak Khemuka
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
@@ -2690,15 +1942,15 @@
       <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
+          <t>PowerCycle
+Rohan Dahima
 27% pred | 27% hist
 [DROP]</t>
         </is>
@@ -2707,7 +1959,7 @@
         <is>
           <t>Barre 57
 Karan Bhatia
-38% pred | 38% hist
+37% pred | 37% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2727,23 +1979,30 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n"/>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-26% pred | 26% hist
-[PROTECT_EXACT]</t>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2758,8 +2017,8 @@
       <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Richard D'Costa
-37% pred | 37% hist
+Simonelle De Vitre
+30% pred | 30% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2767,7 +2026,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -2837,7 +2096,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
@@ -2874,19 +2133,12 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
@@ -2900,20 +2152,20 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-41% pred | 41% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>HIIT
 Richard D'Costa
-59% pred | 59% hist
-[PROTECT_EXACT]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -2924,7 +2176,843 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kwality House, Kemps Corner  |  Class Variety  |  Week of 2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Monday
+4-May</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday
+5-May</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday
+6-May</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Thursday
+7-May</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Friday
+8-May</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Saturday
+9-May</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Sunday
+10-May</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Anisha Shah
+88% pred | 88% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Anisha Shah
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+64% pred | 64% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+40% pred | 40% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>HIIT
+Mrigakshi Jaiswal
+47% pred | 47% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
+Atulan Purohit
+67% pred | 67% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Richard D'Costa
+51% pred | 51% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+62% pred | 62% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+18% pred | 18% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+73% pred | 73% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+28% pred | 28% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Atulan Purohit
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+16% pred | 16% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+27% pred | 27% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+37% pred | 37% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+15% pred | 15% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+41% pred | 41% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Richard D'Costa
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+57% pred | 57% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+43% pred | 43% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+6% pred | 6% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anmol Sharma
+83% pred | 83% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>HIIT
 Richard D'Costa
@@ -2932,7 +3020,24 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H24" s="6" t="n"/>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -64,11 +64,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00831843"/>
+      <color rgb="00374151"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00374151"/>
+      <color rgb="00831843"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -121,12 +121,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD5F0"/>
+        <fgColor rgb="00F0F0F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F5"/>
+        <fgColor rgb="00FFD5F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -573,7 +573,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kwality House, Kemps Corner  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Kwality House, Kemps Corner  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -586,43 +586,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
         <is>
           <t>PowerCycle
 Bret Saldanha
-40% pred | 40% hist
+41% pred | 41% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -702,7 +702,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-64% pred | 64% hist
+63% pred | 63% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -732,34 +732,27 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>HIIT
-Mrigakshi Jaiswal
-47% pred | 47% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Anmol Sharma
+Cauveri Vikrant
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -778,7 +771,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-67% pred | 67% hist
+69% pred | 69% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -797,7 +790,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-51% pred | 51% hist
+64% pred | 64% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -805,7 +798,7 @@
         <is>
           <t>Strength Lab (Full Body)
 Pranjali Jain
-46% pred | 46% hist
+45% pred | 45% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -813,25 +806,25 @@
         <is>
           <t>Barre 57
 Simonelle De Vitre
-54% pred | 54% hist
+56% pred | 56% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
+          <t>Barre 57
+Simonelle De Vitre
+48% pred | 48% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
           <t>FIT
-Mrigakshi Jaiswal
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-24% pred | 24% hist
-[CONSIDER]</t>
+Anmol Sharma
+51% pred | 51% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -865,7 +858,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Back Body Blaze
 Anisha Shah
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
@@ -882,7 +875,14 @@
         </is>
       </c>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+22% pred | 22% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -900,16 +900,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Bret Saldanha
+54% pred | 54% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -926,19 +926,19 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
 Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+33% pred | 33% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Pranjali Jain
-31% pred | 31% hist
+          <t>Cardio Barre
+Simonelle De Vitre
+28% pred | 28% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -946,7 +946,7 @@
         <is>
           <t>Cardio Barre
 Atulan Purohit
-39% pred | 39% hist
+40% pred | 40% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -960,7 +960,14 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H12" s="6" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -977,7 +984,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Barre 57
@@ -986,18 +1000,18 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-54% pred | 54% hist
-[PROTECT_EXACT]</t>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+21% pred | 21% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Reshma Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
@@ -1011,15 +1025,15 @@
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
@@ -1029,7 +1043,14 @@
         </is>
       </c>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
@@ -1088,8 +1109,8 @@
       <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
-40% pred | 40% hist
+Simonelle De Vitre
+29% pred | 29% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1113,7 +1134,7 @@
         <is>
           <t>Barre 57
 Karan Bhatia
-37% pred | 37% hist
+38% pred | 38% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1143,7 +1164,7 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Simran Dutt
@@ -1151,21 +1172,28 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+26% pred | 26% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Simonelle De Vitre
-30% pred | 30% hist
+Richard D'Costa
+37% pred | 37% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1248,12 +1276,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1272,12 +1300,12 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simonelle De Vitre
-6% pred | 6% hist
-[CONSIDER]</t>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F23" s="6" t="n"/>
@@ -1299,20 +1327,13 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>HIIT
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
 Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+59% pred | 59% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -1356,7 +1377,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kwality House, Kemps Corner  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Kwality House, Kemps Corner  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1369,43 +1390,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -1453,14 +1474,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Mrigakshi Jaiswal
-58% pred | 58% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
@@ -1484,7 +1498,7 @@
         <is>
           <t>PowerCycle
 Karan Bhatia
-76% pred | 76% hist
+77% pred | 77% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1492,7 +1506,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-64% pred | 64% hist
+63% pred | 63% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1516,37 +1530,30 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+          <t>Barre 57
+Simonelle De Vitre
+40% pred | 40% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -1561,7 +1568,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-67% pred | 67% hist
+69% pred | 69% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1580,7 +1587,7 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
-51% pred | 51% hist
+64% pred | 64% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1596,25 +1603,25 @@
         <is>
           <t>Barre 57
 Simonelle De Vitre
-54% pred | 54% hist
+56% pred | 56% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
+          <t>Barre 57
+Simonelle De Vitre
+48% pred | 48% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
           <t>FIT
-Mrigakshi Jaiswal
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-24% pred | 24% hist
-[CONSIDER]</t>
+Anmol Sharma
+51% pred | 51% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -1628,11 +1635,11 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-38% pred | 38% hist
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+61% pred | 61% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1646,24 +1653,31 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-18% pred | 18% hist
-[PROTECT_EXACT]</t>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Barre 57
 Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+22% pred | 22% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -1697,9 +1711,9 @@
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Reshma Sharma
-71% pred | 71% hist
-[CONSIDER]</t>
+Rohan Dahima
+73% pred | 73% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -1709,39 +1723,25 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B12" s="6" t="n"/>
       <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
-Raunak Khemuka
+Simonelle De Vitre
 28% pred | 28% hist
-[INCLUDE]</t>
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Atulan Purohit
-39% pred | 39% hist
+40% pred | 40% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1750,14 +1750,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -1765,9 +1758,9 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Amped Up!
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
 Richard D'Costa
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
@@ -1781,15 +1774,64 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Amped Up!
 Anisha Shah
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+21% pred | 21% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -1797,70 +1839,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Mrigakshi Jaiswal
-54% pred | 54% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1869,12 +1848,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -1950,24 +1929,24 @@
       <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
-Rohan Dahima
-27% pred | 27% hist
-[DROP]</t>
+Raunak Khemuka
+20% pred | 20% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
-37% pred | 37% hist
+38% pred | 38% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Simran Dutt
-21% pred | 21% hist
+Richard D'Costa
+31% pred | 31% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1979,7 +1958,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anmol Sharma
@@ -1997,18 +1976,18 @@
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Bret Saldanha
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -2017,8 +1996,8 @@
       <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Simonelle De Vitre
-30% pred | 30% hist
+Richard D'Costa
+37% pred | 37% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2083,8 +2062,8 @@
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-44% pred | 44% hist
+Simran Dutt
+57% pred | 57% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2101,12 +2080,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2133,8 +2112,22 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>HIIT
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>HIIT
+Karan Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
@@ -2152,18 +2145,18 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>HIIT
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>FIT
 Richard D'Costa
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Simran Dutt
+Bret Saldanha
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -2209,7 +2202,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kwality House, Kemps Corner  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Kwality House, Kemps Corner  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2222,43 +2215,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -2290,11 +2283,11 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-40% pred | 40% hist
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+46% pred | 46% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2306,15 +2299,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
 Mrigakshi Jaiswal
-58% pred | 58% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n"/>
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
     </row>
@@ -2331,7 +2324,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-64% pred | 64% hist
+63% pred | 63% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2363,36 +2356,22 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>HIIT
-Mrigakshi Jaiswal
-47% pred | 47% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+          <t>PowerCycle
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -2407,7 +2386,7 @@
         <is>
           <t>Strength Lab (Pull)
 Atulan Purohit
-67% pred | 67% hist
+69% pred | 69% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2426,41 +2405,41 @@
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
+64% pred | 64% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Atulan Purohit
+71% pred | 71% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+48% pred | 48% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
 51% pred | 51% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-54% pred | 54% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-62% pred | 62% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -2474,11 +2453,11 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-38% pred | 38% hist
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
+Vivaran Dhasmana
+61% pred | 61% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2492,22 +2471,15 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Anisha Shah
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -2520,10 +2492,10 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+          <t>Barre 57
+Cauveri Vikrant
+22% pred | 22% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -2557,9 +2529,9 @@
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Rohan Dahima
-73% pred | 73% hist
-[PROTECT_EXACT]</t>
+Reshma Sharma
+71% pred | 71% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2541,12 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
 Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+33% pred | 33% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2587,23 +2559,30 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Atulan Purohit
+          <t>Cardio Barre
+Anisha Shah
 39% pred | 39% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simran Dutt
+76% pred | 76% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Raunak Khemuka
@@ -2622,30 +2601,44 @@
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
+Atulan Purohit
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+21% pred | 21% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>FIT
 Reshma Sharma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-16% pred | 16% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2656,15 +2649,15 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Amped Up!
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+Vivaran Dhasmana
+23% pred | 23% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
     </row>
@@ -2674,46 +2667,46 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
 Richard D'Costa
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>FIT
-Atulan Purohit
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+          <t>Cardio Barre
+Karan Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
+Simran Dutt
 36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>FIT
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -2773,8 +2766,8 @@
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
-40% pred | 40% hist
+Simonelle De Vitre
+29% pred | 29% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2798,15 +2791,15 @@
         <is>
           <t>Barre 57
 Karan Bhatia
-37% pred | 37% hist
+38% pred | 38% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Richard D'Costa
-31% pred | 31% hist
+Simran Dutt
+21% pred | 21% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2818,10 +2811,10 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Simonelle De Vitre
+Anmol Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -2835,8 +2828,7 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Simran Dutt
@@ -2844,20 +2836,21 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
-41% pred | 41% hist
+Richard D'Costa
+37% pred | 37% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2870,14 +2863,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="8" t="inlineStr">
@@ -2929,8 +2915,8 @@
       <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Simran Dutt
-57% pred | 57% hist
+Rohan Dahima
+44% pred | 44% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2947,12 +2933,12 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -2979,14 +2965,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="6" t="n"/>
     </row>
@@ -2996,14 +2975,7 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B25" s="6" t="n"/>
       <c r="C25" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
@@ -3012,7 +2984,7 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>HIIT
 Richard D'Costa
@@ -3020,7 +2992,7 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Bret Saldanha
@@ -3030,13 +3002,20 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n"/>
+          <t>Cardio Barre
+Karan Bhatia
+67% pred | 67% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H25" s="6" t="n"/>
     </row>
   </sheetData>

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -59,16 +59,16 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="00831843"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
     <font>
       <color rgb="00374151"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="00831843"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -116,17 +116,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFD5F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD5F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -184,10 +184,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,14 @@
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -711,7 +718,7 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -726,30 +733,37 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+          <t>Cardio Barre Plus
 Bret Saldanha
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+54% pred | 54% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Cauveri Vikrant
@@ -760,33 +774,12 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Atulan Purohit
-69% pred | 69% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Push)
 Richard D'Costa
@@ -794,79 +787,72 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Pranjali Jain
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-48% pred | 48% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+Atulan Purohit
+71% pred | 71% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+62% pred | 62% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Anmol Sharma
-51% pred | 51% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -874,25 +860,25 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-22% pred | 22% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
@@ -900,91 +886,82 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+73% pred | 73% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+28% pred | 28% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Bret Saldanha
+Anisha Shah
 54% pred | 54% hist
-[DROP]</t>
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Reshma Sharma
-71% pred | 71% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+63% pred | 63% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-33% pred | 33% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simonelle De Vitre
-28% pred | 28% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simran Dutt
-76% pred | 76% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-43% pred | 43% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Amped Up!
 Anisha Shah
@@ -992,7 +969,16 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -1000,41 +986,27 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Mrigakshi Jaiswal
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Mrigakshi Jaiswal
@@ -1042,12 +1014,47 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+73% pred | 73% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-36% pred | 36% hist
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1056,7 +1063,7 @@
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
@@ -1064,11 +1071,11 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+28% pred | 28% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1077,7 +1084,7 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -1085,28 +1092,7 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simonelle De Vitre
@@ -1114,39 +1100,39 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Simonelle De Vitre
-27% pred | 27% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
 38% pred | 38% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Simonelle De Vitre
@@ -1154,172 +1140,165 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-26% pred | 26% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>FIT
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-37% pred | 37% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n"/>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Richard D'Costa
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
 Anmol Sharma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+74% pred | 74% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
 Richard D'Costa
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+37% pred | 37% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Karan Bhatia
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
+          <t>FIT
 Simran Dutt
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-43% pred | 43% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="7" t="inlineStr">
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anmol Sharma
@@ -1327,25 +1306,32 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Richard D'Costa
-59% pred | 59% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+41% pred | 41% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+32% pred | 32% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
-Karan Bhatia
+Simonelle De Vitre
 67% pred | 67% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1457,7 +1443,14 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
           <t>FIT
@@ -1474,7 +1467,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
@@ -1515,45 +1515,52 @@
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>FIT
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-40% pred | 40% hist
-[CONSIDER]</t>
+          <t>Cardio Barre Plus
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Mrigakshi Jaiswal
+47% pred | 47% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -1578,19 +1585,12 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-64% pred | 64% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -1602,7 +1602,7 @@
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Simonelle De Vitre
+Karan Bhatia
 56% pred | 56% hist
 [PROTECT_EXACT]</t>
         </is>
@@ -1610,18 +1610,18 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-48% pred | 48% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
           <t>FIT
+Mrigakshi Jaiswal
+62% pred | 62% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Anmol Sharma
-51% pred | 51% hist
-[INCLUDE]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -1635,11 +1635,11 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-61% pred | 61% hist
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1648,38 +1648,31 @@
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Push)
 Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+18% pred | 18% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-22% pred | 22% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
@@ -1718,18 +1711,25 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+46% pred | 46% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
-Simonelle De Vitre
+Raunak Khemuka
 28% pred | 28% hist
-[CONSIDER]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1753,19 +1753,12 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1774,64 +1767,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -1839,6 +1776,48 @@
 [CONSIDER]</t>
         </is>
       </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Rohan Dahima
+23% pred | 23% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -1921,23 +1900,23 @@
       <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-20% pred | 20% hist
-[CONSIDER]</t>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+67% pred | 67% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
+Simran Dutt
 38% pred | 38% hist
 [CONSIDER]</t>
         </is>
@@ -1958,7 +1937,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anmol Sharma
@@ -1970,34 +1949,34 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+26% pred | 26% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>FIT
 Bret Saldanha
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Richard D'Costa
-37% pred | 37% hist
+Simonelle De Vitre
+30% pred | 30% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2005,22 +1984,22 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Richard D'Costa
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
@@ -2062,8 +2041,8 @@
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Simran Dutt
-57% pred | 57% hist
+Pranjali Jain
+64% pred | 64% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2075,17 +2054,17 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Anmol Sharma
+74% pred | 74% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2099,8 +2078,8 @@
       <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Barre 57
-Simran Dutt
-43% pred | 43% hist
+Richard D'Costa
+37% pred | 37% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2112,26 +2091,12 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Karan Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
@@ -2140,33 +2105,33 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Anmol Sharma
+Simonelle De Vitre
 83% pred | 83% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simran Dutt
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Karan Bhatia
-67% pred | 67% hist
-[CONSIDER]</t>
+          <t>Barre 57
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="G24" s="6" t="n"/>
@@ -2186,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2299,7 +2264,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
@@ -2328,41 +2300,41 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n"/>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-40% pred | 40% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>HIIT
+Mrigakshi Jaiswal
+47% pred | 47% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2396,19 +2368,12 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Richard D'Costa
-64% pred | 64% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
@@ -2421,27 +2386,20 @@
         <is>
           <t>Barre 57
 Simonelle De Vitre
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
+46% pred | 46% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-48% pred | 48% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
           <t>FIT
-Anmol Sharma
-51% pred | 51% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+Mrigakshi Jaiswal
+62% pred | 62% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
@@ -2453,11 +2411,11 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Push)
-Vivaran Dhasmana
-61% pred | 61% hist
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2466,17 +2424,17 @@
       <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Pull)
 Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C10" s="6" t="n"/>
@@ -2492,10 +2450,10 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>FIT
 Cauveri Vikrant
-22% pred | 22% hist
-[CONSIDER]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -2529,51 +2487,44 @@
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Full Body)
-Reshma Sharma
-71% pred | 71% hist
-[CONSIDER]</t>
+Rohan Dahima
+73% pred | 73% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-33% pred | 33% hist
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Raunak Khemuka
+28% pred | 28% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
-Simonelle De Vitre
-28% pred | 28% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Anisha Shah
-39% pred | 39% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n"/>
+Atulan Purohit
+40% pred | 40% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2582,7 +2533,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Raunak Khemuka
@@ -2592,12 +2543,19 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Anisha Shah
+10% pred | 10% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2606,114 +2564,100 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Amped Up!
+Anisha Shah
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Mrigakshi Jaiswal
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Amped Up!
-Vivaran Dhasmana
-23% pred | 23% hist
-[DROP]</t>
-        </is>
-      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+73% pred | 73% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Pull)
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
@@ -2721,11 +2665,11 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-31% pred | 31% hist
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+28% pred | 28% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2734,7 +2678,7 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
@@ -2742,28 +2686,7 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simonelle De Vitre
@@ -2771,177 +2694,163 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anmol Sharma
+39% pred | 39% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+100% pred | 100% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Simonelle De Vitre
-27% pred | 27% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-38% pred | 38% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Trainer's Choice
 Simran Dutt
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
 Simonelle De Vitre
-15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
 Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Trainer's Choice
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-37% pred | 37% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
+57% pred | 57% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Richard D'Costa
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
 Anmol Sharma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>FIT
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+74% pred | 74% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -2949,15 +2858,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-43% pred | 43% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+37% pred | 37% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Cardio Barre
 Simonelle De Vitre
@@ -2965,18 +2874,18 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anmol Sharma
@@ -2984,15 +2893,15 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>HIIT
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Simran Dutt
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Bret Saldanha
@@ -3000,15 +2909,15 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-67% pred | 67% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Amped Up!
 Richard D'Costa
@@ -3016,7 +2925,7 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kwality.xlsx
+++ b/outputs/schedule_kwality.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -750,14 +750,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simran Dutt
-40% pred | 40% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
     </row>
@@ -785,7 +778,14 @@
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
@@ -918,7 +918,14 @@
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -927,14 +934,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -1086,20 +1086,20 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
@@ -1107,23 +1107,23 @@
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1137,9 +1137,9 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Karan Bhatia
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
@@ -1165,30 +1165,44 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Karan Bhatia
 41% pred | 41% hist
 [INCLUDE]</t>
@@ -1196,82 +1210,47 @@
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Bret Saldanha
-41% pred | 41% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+44% pred | 44% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-67% pred | 67% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-44% pred | 44% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -1279,7 +1258,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -1287,22 +1266,29 @@
 [INCLUDE]</t>
         </is>
       </c>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
 Mrigakshi Jaiswal
@@ -1310,7 +1296,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Simonelle De Vitre
@@ -1318,18 +1304,18 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1337,7 +1323,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Karan Bhatia
@@ -1345,8 +1331,8 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Richard D'Costa
@@ -1354,15 +1340,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1370,34 +1356,34 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Karan Bhatia
+Simonelle De Vitre
 26% pred | 26% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Simonelle De Vitre
+Simran Dutt
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -1405,10 +1391,10 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1416,16 +1402,16 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -1433,7 +1419,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simran Dutt
@@ -1441,7 +1427,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -1449,7 +1435,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -1457,7 +1443,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simonelle De Vitre
@@ -1465,17 +1451,17 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-    </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
@@ -1483,39 +1469,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Raunak Khemuka
-42% pred | 42% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-    </row>
-    <row r="32" ht="52" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1531,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1614,7 +1572,14 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+13% pred | 13% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D3" s="7" t="n"/>
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="7" t="n"/>
@@ -1627,13 +1592,20 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Bret Saldanha
-41% pred | 41% hist
-[PROTECT_EXACT]</t>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+43% pred | 43% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anisha Shah
+82% pred | 82% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1716,20 +1688,13 @@
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Vivaran Dhasmana
-61% pred | 61% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simran Dutt
-40% pred | 40% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+          <t>PowerCycle
+Rohan Dahima
+90% pred | 90% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
     </row>
@@ -1757,7 +1722,14 @@
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
@@ -1890,7 +1862,14 @@
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2051,58 +2030,121 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Anisha Shah
-28% pred | 28% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Anisha Shah
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karan Bhatia
@@ -2111,23 +2153,23 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-67% pred | 67% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -2135,7 +2177,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2143,16 +2185,16 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>FIT
 Anisha Shah
@@ -2160,7 +2202,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simran Dutt
@@ -2168,11 +2210,11 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anmol Sharma
@@ -2181,16 +2223,16 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze Express
 Mrigakshi Jaiswal
@@ -2198,7 +2240,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Simonelle De Vitre
@@ -2206,18 +2248,18 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2225,7 +2267,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Karan Bhatia
@@ -2233,8 +2275,8 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Richard D'Costa
@@ -2242,15 +2284,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2258,34 +2300,34 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Karan Bhatia
+Simonelle De Vitre
 26% pred | 26% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Vivaran Dhasmana
+Simran Dutt
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -2293,10 +2335,10 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2304,16 +2346,16 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Trainer's Choice
 Anisha Shah
@@ -2321,7 +2363,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simran Dutt
@@ -2329,7 +2371,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Anmol Sharma
@@ -2337,7 +2379,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Strength Lab (Pull)
 Mrigakshi Jaiswal
@@ -2345,7 +2387,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Simonelle De Vitre
@@ -2353,17 +2395,17 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
@@ -2371,18 +2413,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Raunak Khemuka
-42% pred | 42% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2603,14 +2638,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simran Dutt
-40% pred | 40% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
     </row>
@@ -2638,7 +2666,14 @@
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
@@ -2771,7 +2806,14 @@
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2780,14 +2822,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="H12" s="7" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -2960,7 +2995,7 @@
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="7" t="n"/>
@@ -2972,7 +3007,7 @@
       <c r="H19" s="6" t="inlineStr">
         <is>
           <t>FIT
-Bret Saldanha
+Raunak Khemuka
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -2981,7 +3016,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B20" s="7" t="n"/>
@@ -2989,20 +3024,20 @@
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Strength Lab (Full Body)
-Richard D'Costa
-28% pred | 28% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
@@ -3010,13 +3045,20 @@
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Strength Lab (Full Body)
+Richard D'Costa
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>PowerCycle Express
-Karan Bhatia
-41% pred | 41% hist
-[INCLUDE]</t>
+          <t>PowerCycle
+Anmol Sharma
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -3041,15 +3083,15 @@
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Simonelle De Vitre
-29% pred | 29% hist
+Simran Dutt
+34% pred | 34% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Bret Saldanha
+Karan Bhatia
 41% pred | 41% hist
 [INCLUDE]</t>
         </is>
@@ -3116,7 +3158,14 @@
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -3199,7 +3248,7 @@
       <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
-Karan Bhatia
+Simonelle De Vitre
 26% pred | 26% hist
 [INCLUDE]</t>
         </is>
@@ -3209,7 +3258,7 @@
       <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Simonelle De Vitre
+Simran Dutt
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -3310,14 +3359,7 @@
       </c>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Raunak Khemuka
-42% pred | 42% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
     </row>
